--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.80133923233502</v>
+        <v>2.730217625254442</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86301426198769</v>
+        <v>2.740239817572999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F2" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.45035467634504</v>
+        <v>5.76068263490607</v>
       </c>
       <c r="D3" t="n">
-        <v>35.21984348085502</v>
+        <v>5.723224565638941</v>
       </c>
       <c r="E3" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F3" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.75928382001507</v>
+        <v>3.69838362075245</v>
       </c>
       <c r="D4" t="n">
-        <v>17.67059704707229</v>
+        <v>2.871472020149247</v>
       </c>
       <c r="E4" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F4" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.76089452343382</v>
+        <v>3.536145360057995</v>
       </c>
       <c r="D5" t="n">
-        <v>20.89853323936981</v>
+        <v>3.396011651397595</v>
       </c>
       <c r="E5" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F5" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.06975030701331</v>
+        <v>5.861334424889662</v>
       </c>
       <c r="D6" t="n">
-        <v>34.12187781097369</v>
+        <v>5.544805144283226</v>
       </c>
       <c r="E6" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F6" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.51558175465602</v>
+        <v>4.471282035131603</v>
       </c>
       <c r="D7" t="n">
-        <v>25.73080338540145</v>
+        <v>4.181255550127736</v>
       </c>
       <c r="E7" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F7" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.29977814230653</v>
+        <v>7.198713948124811</v>
       </c>
       <c r="D8" t="n">
-        <v>35.84134010115481</v>
+        <v>5.824217766437657</v>
       </c>
       <c r="E8" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F8" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.4566373324226</v>
+        <v>6.411703566518673</v>
       </c>
       <c r="D9" t="n">
-        <v>40.61065313853786</v>
+        <v>6.599231135012402</v>
       </c>
       <c r="E9" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F9" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.15885002206007</v>
+        <v>5.388313128584761</v>
       </c>
       <c r="D10" t="n">
-        <v>32.19864674227284</v>
+        <v>5.232280095619337</v>
       </c>
       <c r="E10" t="n">
-        <v>8.597476939956866</v>
+        <v>1.397090002742991</v>
       </c>
       <c r="F10" t="n">
-        <v>8.221703884768539</v>
+        <v>1.336026881274888</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
